--- a/jadwal_grid_genap_2025-2026 (6).xlsx
+++ b/jadwal_grid_genap_2025-2026 (6).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muhyu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_BAF7C117F6287D489661027368509733A02CCD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91A7397-CFD4-483C-8ECF-7D7F7BEF009A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,676 +91,676 @@
     <t>SENIN</t>
   </si>
   <si>
+    <t>28V</t>
+  </si>
+  <si>
     <t>16I</t>
   </si>
   <si>
+    <t>36W</t>
+  </si>
+  <si>
+    <t>22C</t>
+  </si>
+  <si>
+    <t>21X</t>
+  </si>
+  <si>
+    <t>18I</t>
+  </si>
+  <si>
+    <t>25K</t>
+  </si>
+  <si>
+    <t>8C</t>
+  </si>
+  <si>
+    <t>34U</t>
+  </si>
+  <si>
+    <t>32U</t>
+  </si>
+  <si>
+    <t>11I</t>
+  </si>
+  <si>
+    <t>27X</t>
+  </si>
+  <si>
+    <t>33AD</t>
+  </si>
+  <si>
+    <t>2A</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Mehram,S.Pd.,M.AP.</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Al-Quran Hadits</t>
+  </si>
+  <si>
+    <t>Senin</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>H. Muksan,S.Pd.I.,M.Pd</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>Bahasa Inggris TL</t>
+  </si>
+  <si>
+    <t>Jam Ke    Waktu</t>
+  </si>
+  <si>
+    <t>24D</t>
+  </si>
+  <si>
+    <t>26H</t>
+  </si>
+  <si>
+    <t>35AF</t>
+  </si>
+  <si>
+    <t>15G</t>
+  </si>
+  <si>
+    <t>9S</t>
+  </si>
+  <si>
+    <t>13Q</t>
+  </si>
+  <si>
+    <t>23N</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Azanul Haq,S.Ag.,M.Pd</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>Bahasa Arab TL</t>
+  </si>
+  <si>
+    <t>07:30:00 - 08:15:00</t>
+  </si>
+  <si>
+    <t>31J</t>
+  </si>
+  <si>
+    <t>22A</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Mazaharudin, S.Ag</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>Bahasa Asing</t>
+  </si>
+  <si>
+    <t>08:15:00 - 09:00:00</t>
+  </si>
+  <si>
+    <t>32F</t>
+  </si>
+  <si>
+    <t>30R</t>
+  </si>
+  <si>
+    <t>7B</t>
+  </si>
+  <si>
+    <t>19P</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Apnadi, S.Pd.,M.Pd</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>Informatika</t>
+  </si>
+  <si>
+    <t>09:00:00 - 09:45:00</t>
+  </si>
+  <si>
+    <t>9Y</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>15Z</t>
+  </si>
+  <si>
+    <t>5G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Lalu Zulkifli,S.Pd, M. Pd</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>Informatika TL</t>
+  </si>
+  <si>
+    <t>09:45:00 - 10:30:00</t>
+  </si>
+  <si>
+    <t>6W</t>
+  </si>
+  <si>
+    <t>14G</t>
+  </si>
+  <si>
+    <t>10W</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>H. Fathul Arifin, S. Ag</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>Mulok (Muhadasah)</t>
+  </si>
+  <si>
+    <t>10:45:00 - 11:30:00</t>
+  </si>
+  <si>
+    <t>33AG</t>
+  </si>
+  <si>
+    <t>20E</t>
+  </si>
+  <si>
+    <t>12H</t>
+  </si>
+  <si>
+    <t>3E</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Muhayan.S.Ag.,M.Pd</t>
+  </si>
+  <si>
+    <t>AG</t>
+  </si>
+  <si>
+    <t>KKA</t>
+  </si>
+  <si>
+    <t>11:30:00 - 12:15:00</t>
+  </si>
+  <si>
+    <t>17E</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Bq. Dewi Ratnasari,S.Sos</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Fikih</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:00:00</t>
+  </si>
+  <si>
+    <t>SELASA</t>
+  </si>
+  <si>
+    <t>37H</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Fahilwaty,S.Pd</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Akidah Akhlak</t>
+  </si>
+  <si>
+    <t>13:15:00 - 14:00:00</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Nurman, S.Pd.</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>SKI</t>
+  </si>
+  <si>
+    <t>14:00:00 - 14:45:00</t>
+  </si>
+  <si>
+    <t>38F</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Muhammad Yusri, SS. M. Pd</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Bahasa Arab</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Lalu Muhammad Zaenuddin, S.E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Pendidikan Pancasila</t>
+  </si>
+  <si>
+    <t>Selasa-Kamis, Sabtu</t>
+  </si>
+  <si>
+    <t>20AB</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Ruslan, S.Pd.</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Bahasa Indonesia</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Dian Aprila Diniarti, M.Pd</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Bahasa Inggris</t>
+  </si>
+  <si>
+    <t>07:15:00 - 08:00:00</t>
+  </si>
+  <si>
+    <t>21M</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Suriati,S.Pd</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Matematika</t>
+  </si>
+  <si>
+    <t>08:00:00 - 08:45:00</t>
+  </si>
+  <si>
+    <t>34L</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Nurfitri Hidayati, S.Pd.I., M.Hum</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Sejarah</t>
+  </si>
+  <si>
+    <t>08:45:00 - 09:30:00</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Arya Gustu Pradana, S.Pd</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Penjaskes</t>
+  </si>
+  <si>
+    <t>09:30:00 - 10:15:00</t>
+  </si>
+  <si>
+    <t>RABU</t>
+  </si>
+  <si>
+    <t>32I</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Zamzami Azwar, S.Sy.</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Seni Budaya</t>
+  </si>
+  <si>
+    <t>10:30:00 - 11:15:00</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Badri, S.Pd.I</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Prakarya dan Kewirausahaan</t>
+  </si>
+  <si>
+    <t>11:15:00 - 12:00:00</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Dina Marselina, S.Pd</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Ilmu Tafsir</t>
+  </si>
+  <si>
+    <t>12:00:00 - 12:45:00</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Muhammad Zulkifli, S.Pd.I</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>Ilmu Hadits</t>
+  </si>
+  <si>
+    <t>13:00:00 - 13:45:00</t>
+  </si>
+  <si>
     <t>36M</t>
   </si>
   <si>
-    <t>21X</t>
-  </si>
-  <si>
-    <t>20E</t>
-  </si>
-  <si>
-    <t>28V</t>
-  </si>
-  <si>
-    <t>34U</t>
-  </si>
-  <si>
-    <t>32U</t>
-  </si>
-  <si>
-    <t>24D</t>
-  </si>
-  <si>
-    <t>27X</t>
-  </si>
-  <si>
-    <t>18I</t>
-  </si>
-  <si>
-    <t>23N</t>
-  </si>
-  <si>
-    <t>25K</t>
-  </si>
-  <si>
-    <t>11I</t>
-  </si>
-  <si>
-    <t>13Q</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Mehram,S.Pd.,M.AP.</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Al-Quran Hadits</t>
-  </si>
-  <si>
-    <t>Senin</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>H. Muksan,S.Pd.I.,M.Pd</t>
-  </si>
-  <si>
-    <t>AA</t>
-  </si>
-  <si>
-    <t>Bahasa Inggris TL</t>
-  </si>
-  <si>
-    <t>Jam Ke    Waktu</t>
-  </si>
-  <si>
-    <t>26H</t>
-  </si>
-  <si>
-    <t>35AF</t>
-  </si>
-  <si>
-    <t>36W</t>
-  </si>
-  <si>
-    <t>9S</t>
-  </si>
-  <si>
-    <t>31J</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Azanul Haq,S.Ag.,M.Pd</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>Bahasa Arab TL</t>
-  </si>
-  <si>
-    <t>07:30:00 - 08:15:00</t>
-  </si>
-  <si>
-    <t>7B</t>
-  </si>
-  <si>
-    <t>4B</t>
-  </si>
-  <si>
-    <t>21M</t>
-  </si>
-  <si>
-    <t>33AD</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Mazaharudin, S.Ag</t>
-  </si>
-  <si>
-    <t>AC</t>
-  </si>
-  <si>
-    <t>Bahasa Asing</t>
-  </si>
-  <si>
-    <t>08:15:00 - 09:00:00</t>
-  </si>
-  <si>
-    <t>32F</t>
-  </si>
-  <si>
-    <t>30R</t>
-  </si>
-  <si>
-    <t>8C</t>
-  </si>
-  <si>
-    <t>5G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Apnadi, S.Pd.,M.Pd</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>Informatika</t>
-  </si>
-  <si>
-    <t>09:00:00 - 09:45:00</t>
-  </si>
-  <si>
-    <t>14G</t>
-  </si>
-  <si>
-    <t>15G</t>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Mudepan, S.Ag</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Ushul Fikih</t>
+  </si>
+  <si>
+    <t>13:45:00 - 14:30:00</t>
+  </si>
+  <si>
+    <t>23O</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Nihun, S.Pd.I</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>Ekonomi</t>
+  </si>
+  <si>
+    <t>35L</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>L. M. Alviadi, S.Pd.</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Geografi</t>
+  </si>
+  <si>
+    <t>Jumat</t>
+  </si>
+  <si>
+    <t>3AB</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Diana Rahayu, S.Pd.</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Sosiologi</t>
+  </si>
+  <si>
+    <t>7A</t>
   </si>
   <si>
     <t>36L</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Lalu Zulkifli,S.Pd, M. Pd</t>
-  </si>
-  <si>
-    <t>AE</t>
-  </si>
-  <si>
-    <t>Informatika TL</t>
-  </si>
-  <si>
-    <t>09:45:00 - 10:30:00</t>
-  </si>
-  <si>
-    <t>19P</t>
-  </si>
-  <si>
-    <t>10W</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>H. Fathul Arifin, S. Ag</t>
-  </si>
-  <si>
-    <t>AF</t>
-  </si>
-  <si>
-    <t>Mulok (Muhadasah)</t>
-  </si>
-  <si>
-    <t>10:45:00 - 11:30:00</t>
-  </si>
-  <si>
-    <t>6W</t>
-  </si>
-  <si>
-    <t>22A</t>
-  </si>
-  <si>
-    <t>2A</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Muhayan.S.Ag.,M.Pd</t>
-  </si>
-  <si>
-    <t>AG</t>
-  </si>
-  <si>
-    <t>KKA</t>
-  </si>
-  <si>
-    <t>11:30:00 - 12:15:00</t>
-  </si>
-  <si>
-    <t>17E</t>
-  </si>
-  <si>
-    <t>33AG</t>
-  </si>
-  <si>
-    <t>12H</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Bq. Dewi Ratnasari,S.Sos</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Fikih</t>
-  </si>
-  <si>
-    <t>12:15:00 - 13:00:00</t>
-  </si>
-  <si>
-    <t>SELASA</t>
-  </si>
-  <si>
-    <t>22C</t>
-  </si>
-  <si>
-    <t>32I</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Fahilwaty,S.Pd</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Akidah Akhlak</t>
-  </si>
-  <si>
-    <t>13:15:00 - 14:00:00</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Nurman, S.Pd.</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>SKI</t>
-  </si>
-  <si>
-    <t>14:00:00 - 14:45:00</t>
-  </si>
-  <si>
-    <t>37H</t>
-  </si>
-  <si>
-    <t>20AB</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Muhammad Yusri, SS. M. Pd</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>Bahasa Arab</t>
-  </si>
-  <si>
-    <t>38F</t>
-  </si>
-  <si>
-    <t>34L</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Lalu Muhammad Zaenuddin, S.E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Pendidikan Pancasila</t>
-  </si>
-  <si>
-    <t>Selasa-Kamis, Sabtu</t>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Siti Rohyatul Uyuni, S. Pd</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Sejarah TL</t>
+  </si>
+  <si>
+    <t>KAMIS</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Saepul, S.Pd</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>Matematika TL</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Fathurrahman, S.Pd</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Fisika</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Hidayatul Adniyah, S.Pd</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Biologi</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Junaidi Mariyono, S.Pd.</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Kimia</t>
   </si>
   <si>
     <t>23A</t>
   </si>
   <si>
-    <t>3AB</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Ruslan, S.Pd.</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>Bahasa Indonesia</t>
-  </si>
-  <si>
-    <t>2B</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Dian Aprila Diniarti, M.Pd</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>Bahasa Inggris</t>
-  </si>
-  <si>
-    <t>07:15:00 - 08:00:00</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Suriati,S.Pd</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>Matematika</t>
-  </si>
-  <si>
-    <t>08:00:00 - 08:45:00</t>
-  </si>
-  <si>
-    <t>23O</t>
-  </si>
-  <si>
-    <t>3E</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Nurfitri Hidayati, S.Pd.I., M.Hum</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>Sejarah</t>
-  </si>
-  <si>
-    <t>08:45:00 - 09:30:00</t>
-  </si>
-  <si>
-    <t>35L</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Arya Gustu Pradana, S.Pd</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>Penjaskes</t>
-  </si>
-  <si>
-    <t>09:30:00 - 10:15:00</t>
-  </si>
-  <si>
-    <t>RABU</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Zamzami Azwar, S.Sy.</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Seni Budaya</t>
-  </si>
-  <si>
-    <t>10:30:00 - 11:15:00</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>Badri, S.Pd.I</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>Prakarya dan Kewirausahaan</t>
-  </si>
-  <si>
-    <t>11:15:00 - 12:00:00</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>Dina Marselina, S.Pd</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Ilmu Tafsir</t>
-  </si>
-  <si>
-    <t>12:00:00 - 12:45:00</t>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Baik Rosmala Dewi, S.Pd</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Antropologi</t>
+  </si>
+  <si>
+    <t>28F</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Zaenul Ansori, S.Pd</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>Bahasa Indonesia TL</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Safariah, S.Pd</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Miftahul Jannah, S.Pd</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Wa 'an Hadi, S.Pd</t>
+  </si>
+  <si>
+    <t>JUMAT</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Rokyatul Azmi, S. Pd</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Misriwati, S. Pd</t>
+  </si>
+  <si>
+    <t>SABTU</t>
   </si>
   <si>
     <t>27M</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>Muhammad Zulkifli, S.Pd.I</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>Ilmu Hadits</t>
-  </si>
-  <si>
-    <t>13:00:00 - 13:45:00</t>
-  </si>
-  <si>
-    <t>7A</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Mudepan, S.Ag</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Ushul Fikih</t>
-  </si>
-  <si>
-    <t>13:45:00 - 14:30:00</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>Nihun, S.Pd.I</t>
-  </si>
-  <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>Ekonomi</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>L. M. Alviadi, S.Pd.</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>Geografi</t>
-  </si>
-  <si>
-    <t>Jumat</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Diana Rahayu, S.Pd.</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>Sosiologi</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Siti Rohyatul Uyuni, S. Pd</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>Sejarah TL</t>
-  </si>
-  <si>
-    <t>KAMIS</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Saepul, S.Pd</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>Matematika TL</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Fathurrahman, S.Pd</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Fisika</t>
-  </si>
-  <si>
-    <t>15Z</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Hidayatul Adniyah, S.Pd</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>Biologi</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>Junaidi Mariyono, S.Pd.</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Kimia</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>Baik Rosmala Dewi, S.Pd</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Antropologi</t>
-  </si>
-  <si>
-    <t>9Y</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>Zaenul Ansori, S.Pd</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>Bahasa Indonesia TL</t>
-  </si>
-  <si>
-    <t>28F</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>Safariah, S.Pd</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>Miftahul Jannah, S.Pd</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>Wa 'an Hadi, S.Pd</t>
-  </si>
-  <si>
-    <t>JUMAT</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>Rokyatul Azmi, S. Pd</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>Misriwati, S. Pd</t>
-  </si>
-  <si>
-    <t>SABTU</t>
   </si>
 </sst>
 </file>
@@ -776,12 +776,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -796,8 +802,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1746,44 +1753,44 @@
         <v>47</v>
       </c>
       <c r="D8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s">
         <v>23</v>
       </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
       <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
         <v>27</v>
-      </c>
-      <c r="G8" t="s">
-        <v>48</v>
       </c>
       <c r="H8" t="s">
         <v>49</v>
       </c>
       <c r="I8" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="J8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" t="s">
+        <v>35</v>
+      </c>
+      <c r="P8" t="s">
         <v>34</v>
       </c>
-      <c r="M8" t="s">
-        <v>33</v>
-      </c>
-      <c r="N8" t="s">
-        <v>31</v>
-      </c>
-      <c r="O8" t="s">
-        <v>51</v>
-      </c>
-      <c r="P8" t="s">
-        <v>36</v>
-      </c>
       <c r="Q8" t="s">
         <v>1</v>
       </c>
@@ -1791,19 +1798,19 @@
         <v>1</v>
       </c>
       <c r="S8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="U8" t="s">
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="W8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="X8" t="s">
         <v>1</v>
@@ -1812,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="Z8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AA8" t="s">
         <v>1</v>
@@ -1829,43 +1836,43 @@
         <v>47</v>
       </c>
       <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" t="s">
         <v>23</v>
       </c>
-      <c r="E9" t="s">
-        <v>57</v>
-      </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="H9" t="s">
         <v>49</v>
       </c>
       <c r="I9" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" t="s">
         <v>34</v>
-      </c>
-      <c r="M9" t="s">
-        <v>59</v>
-      </c>
-      <c r="N9" t="s">
-        <v>31</v>
-      </c>
-      <c r="O9" t="s">
-        <v>51</v>
-      </c>
-      <c r="P9" t="s">
-        <v>60</v>
       </c>
       <c r="Q9" t="s">
         <v>1</v>
@@ -1912,43 +1919,43 @@
         <v>66</v>
       </c>
       <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10" t="s">
+        <v>69</v>
+      </c>
+      <c r="N10" t="s">
         <v>30</v>
       </c>
-      <c r="E10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" t="s">
-        <v>50</v>
-      </c>
-      <c r="L10" t="s">
-        <v>67</v>
-      </c>
-      <c r="M10" t="s">
-        <v>59</v>
-      </c>
-      <c r="N10" t="s">
-        <v>68</v>
-      </c>
       <c r="O10" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="P10" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="Q10" t="s">
         <v>1</v>
@@ -1995,43 +2002,43 @@
         <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
         <v>75</v>
       </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" t="s">
         <v>47</v>
       </c>
-      <c r="I11" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
+        <v>69</v>
+      </c>
+      <c r="N11" t="s">
         <v>76</v>
       </c>
-      <c r="L11" t="s">
+      <c r="O11" t="s">
         <v>77</v>
       </c>
-      <c r="M11" t="s">
-        <v>33</v>
-      </c>
-      <c r="N11" t="s">
-        <v>68</v>
-      </c>
-      <c r="O11" t="s">
-        <v>69</v>
-      </c>
       <c r="P11" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="Q11" t="s">
         <v>1</v>
@@ -2040,19 +2047,19 @@
         <v>1</v>
       </c>
       <c r="S11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U11" t="s">
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="W11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X11" t="s">
         <v>1</v>
@@ -2061,7 +2068,7 @@
         <v>4</v>
       </c>
       <c r="Z11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA11" t="s">
         <v>1</v>
@@ -2075,46 +2082,46 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" t="s">
         <v>47</v>
       </c>
-      <c r="E12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" t="s">
-        <v>83</v>
-      </c>
-      <c r="I12" t="s">
-        <v>84</v>
-      </c>
-      <c r="J12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
+        <v>87</v>
+      </c>
+      <c r="M12" t="s">
+        <v>69</v>
+      </c>
+      <c r="N12" t="s">
         <v>76</v>
       </c>
-      <c r="L12" t="s">
-        <v>30</v>
-      </c>
-      <c r="M12" t="s">
-        <v>33</v>
-      </c>
-      <c r="N12" t="s">
-        <v>68</v>
-      </c>
       <c r="O12" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="P12" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="Q12" t="s">
         <v>1</v>
@@ -2123,19 +2130,19 @@
         <v>1</v>
       </c>
       <c r="S12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="T12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="U12" t="s">
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="W12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X12" t="s">
         <v>1</v>
@@ -2144,7 +2151,7 @@
         <v>5</v>
       </c>
       <c r="Z12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AA12" t="s">
         <v>1</v>
@@ -2158,46 +2165,46 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" t="s">
         <v>67</v>
       </c>
-      <c r="D13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" t="s">
-        <v>51</v>
-      </c>
       <c r="H13" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J13" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="K13" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="L13" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="M13" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="N13" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O13" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="P13" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="Q13" t="s">
         <v>1</v>
@@ -2206,19 +2213,19 @@
         <v>1</v>
       </c>
       <c r="S13" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="T13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="U13" t="s">
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="W13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="X13" t="s">
         <v>1</v>
@@ -2227,7 +2234,7 @@
         <v>6</v>
       </c>
       <c r="Z13" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AA13" t="s">
         <v>1</v>
@@ -2241,46 +2248,46 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" t="s">
-        <v>57</v>
+        <v>85</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="G14" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="H14" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="I14" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J14" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="K14" t="s">
         <v>48</v>
       </c>
       <c r="L14" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="M14" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="N14" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O14" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="P14" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="Q14" t="s">
         <v>1</v>
@@ -2289,19 +2296,19 @@
         <v>1</v>
       </c>
       <c r="S14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="U14" t="s">
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="W14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="X14" t="s">
         <v>1</v>
@@ -2310,7 +2317,7 @@
         <v>7</v>
       </c>
       <c r="Z14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AA14" t="s">
         <v>1</v>
@@ -2318,52 +2325,52 @@
     </row>
     <row r="15" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" t="s">
         <v>23</v>
       </c>
-      <c r="D15" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" t="s">
-        <v>25</v>
-      </c>
       <c r="H15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I15" t="s">
         <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K15" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L15" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="M15" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="N15" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="O15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P15" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="Q15" t="s">
         <v>1</v>
@@ -2372,19 +2379,19 @@
         <v>1</v>
       </c>
       <c r="S15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U15" t="s">
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="W15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="X15" t="s">
         <v>1</v>
@@ -2393,7 +2400,7 @@
         <v>8</v>
       </c>
       <c r="Z15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA15" t="s">
         <v>1</v>
@@ -2407,46 +2414,46 @@
         <v>2</v>
       </c>
       <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" t="s">
         <v>23</v>
       </c>
-      <c r="D16" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" t="s">
-        <v>25</v>
-      </c>
       <c r="H16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I16" t="s">
         <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K16" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L16" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="M16" t="s">
-        <v>68</v>
-      </c>
-      <c r="N16" t="s">
-        <v>108</v>
+        <v>53</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P16" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="Q16" t="s">
         <v>1</v>
@@ -2455,19 +2462,19 @@
         <v>1</v>
       </c>
       <c r="S16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="T16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U16" t="s">
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="W16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X16" t="s">
         <v>1</v>
@@ -2476,7 +2483,7 @@
         <v>9</v>
       </c>
       <c r="Z16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA16" t="s">
         <v>1</v>
@@ -2490,46 +2497,46 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" t="s">
+        <v>120</v>
+      </c>
+      <c r="I17" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" t="s">
+        <v>59</v>
+      </c>
+      <c r="K17" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" t="s">
+        <v>48</v>
+      </c>
+      <c r="M17" t="s">
+        <v>53</v>
+      </c>
+      <c r="N17" t="s">
         <v>23</v>
       </c>
-      <c r="F17" t="s">
-        <v>119</v>
-      </c>
-      <c r="G17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" t="s">
-        <v>47</v>
-      </c>
-      <c r="J17" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" t="s">
-        <v>36</v>
-      </c>
-      <c r="L17" t="s">
-        <v>76</v>
-      </c>
-      <c r="M17" t="s">
-        <v>68</v>
-      </c>
-      <c r="N17" t="s">
-        <v>120</v>
-      </c>
       <c r="O17" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="P17" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="Q17" t="s">
         <v>1</v>
@@ -2573,73 +2580,73 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" t="s">
+        <v>85</v>
+      </c>
+      <c r="H18" t="s">
+        <v>120</v>
+      </c>
+      <c r="I18" t="s">
+        <v>77</v>
+      </c>
+      <c r="J18" t="s">
+        <v>59</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M18" t="s">
+        <v>95</v>
+      </c>
+      <c r="N18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O18" t="s">
+        <v>78</v>
+      </c>
+      <c r="P18" t="s">
         <v>30</v>
       </c>
-      <c r="D18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" t="s">
-        <v>48</v>
-      </c>
-      <c r="I18" t="s">
-        <v>47</v>
-      </c>
-      <c r="J18" t="s">
-        <v>58</v>
-      </c>
-      <c r="K18" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18" t="s">
-        <v>50</v>
-      </c>
-      <c r="M18" t="s">
+      <c r="Q18" t="s">
+        <v>1</v>
+      </c>
+      <c r="R18" t="s">
+        <v>1</v>
+      </c>
+      <c r="S18" t="s">
         <v>125</v>
       </c>
-      <c r="N18" t="s">
-        <v>120</v>
-      </c>
-      <c r="O18" t="s">
-        <v>100</v>
-      </c>
-      <c r="P18" t="s">
+      <c r="T18" t="s">
         <v>126</v>
       </c>
-      <c r="Q18" t="s">
-        <v>1</v>
-      </c>
-      <c r="R18" t="s">
-        <v>1</v>
-      </c>
-      <c r="S18" t="s">
+      <c r="U18" t="s">
+        <v>1</v>
+      </c>
+      <c r="V18" t="s">
         <v>127</v>
       </c>
-      <c r="T18" t="s">
+      <c r="W18" t="s">
         <v>128</v>
       </c>
-      <c r="U18" t="s">
-        <v>1</v>
-      </c>
-      <c r="V18" t="s">
+      <c r="X18" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="s">
         <v>129</v>
-      </c>
-      <c r="W18" t="s">
-        <v>130</v>
-      </c>
-      <c r="X18" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>131</v>
       </c>
       <c r="Z18" t="s">
         <v>1</v>
@@ -2656,67 +2663,67 @@
         <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>132</v>
+        <v>49</v>
       </c>
       <c r="E19" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="F19" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="G19" t="s">
         <v>66</v>
       </c>
       <c r="H19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" t="s">
+        <v>77</v>
+      </c>
+      <c r="J19" t="s">
         <v>48</v>
       </c>
-      <c r="I19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J19" t="s">
-        <v>58</v>
-      </c>
       <c r="K19" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="L19" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="M19" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="N19" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="O19" t="s">
+        <v>78</v>
+      </c>
+      <c r="P19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>1</v>
+      </c>
+      <c r="R19" t="s">
+        <v>1</v>
+      </c>
+      <c r="S19" t="s">
+        <v>131</v>
+      </c>
+      <c r="T19" t="s">
+        <v>132</v>
+      </c>
+      <c r="U19" t="s">
+        <v>1</v>
+      </c>
+      <c r="V19" t="s">
         <v>133</v>
       </c>
-      <c r="P19" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>1</v>
-      </c>
-      <c r="R19" t="s">
-        <v>1</v>
-      </c>
-      <c r="S19" t="s">
+      <c r="W19" t="s">
         <v>134</v>
-      </c>
-      <c r="T19" t="s">
-        <v>135</v>
-      </c>
-      <c r="U19" t="s">
-        <v>1</v>
-      </c>
-      <c r="V19" t="s">
-        <v>136</v>
-      </c>
-      <c r="W19" t="s">
-        <v>137</v>
       </c>
       <c r="X19" t="s">
         <v>1</v>
@@ -2739,43 +2746,43 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="F20" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="G20" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" t="s">
+        <v>77</v>
+      </c>
+      <c r="J20" t="s">
+        <v>48</v>
+      </c>
+      <c r="K20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" t="s">
         <v>67</v>
       </c>
-      <c r="H20" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20" t="s">
-        <v>51</v>
-      </c>
-      <c r="J20" t="s">
-        <v>58</v>
-      </c>
-      <c r="K20" t="s">
-        <v>48</v>
-      </c>
-      <c r="L20" t="s">
-        <v>50</v>
-      </c>
       <c r="M20" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="N20" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="O20" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="P20" t="s">
         <v>30</v>
@@ -2787,28 +2794,28 @@
         <v>1</v>
       </c>
       <c r="S20" t="s">
+        <v>135</v>
+      </c>
+      <c r="T20" t="s">
+        <v>136</v>
+      </c>
+      <c r="U20" t="s">
+        <v>1</v>
+      </c>
+      <c r="V20" t="s">
+        <v>137</v>
+      </c>
+      <c r="W20" t="s">
+        <v>138</v>
+      </c>
+      <c r="X20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="s">
         <v>139</v>
-      </c>
-      <c r="T20" t="s">
-        <v>140</v>
-      </c>
-      <c r="U20" t="s">
-        <v>1</v>
-      </c>
-      <c r="V20" t="s">
-        <v>141</v>
-      </c>
-      <c r="W20" t="s">
-        <v>142</v>
-      </c>
-      <c r="X20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y20">
-        <v>1</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>143</v>
       </c>
       <c r="AA20" t="s">
         <v>1</v>
@@ -2822,46 +2829,46 @@
         <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="F21" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G21" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="H21" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="I21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J21" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K21" t="s">
         <v>50</v>
       </c>
       <c r="L21" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M21" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N21" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="O21" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="P21" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Q21" t="s">
         <v>1</v>
@@ -2870,19 +2877,19 @@
         <v>1</v>
       </c>
       <c r="S21" t="s">
+        <v>141</v>
+      </c>
+      <c r="T21" t="s">
+        <v>142</v>
+      </c>
+      <c r="U21" t="s">
+        <v>1</v>
+      </c>
+      <c r="V21" t="s">
+        <v>143</v>
+      </c>
+      <c r="W21" t="s">
         <v>144</v>
-      </c>
-      <c r="T21" t="s">
-        <v>145</v>
-      </c>
-      <c r="U21" t="s">
-        <v>1</v>
-      </c>
-      <c r="V21" t="s">
-        <v>146</v>
-      </c>
-      <c r="W21" t="s">
-        <v>147</v>
       </c>
       <c r="X21" t="s">
         <v>1</v>
@@ -2891,7 +2898,7 @@
         <v>2</v>
       </c>
       <c r="Z21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AA21" t="s">
         <v>1</v>
@@ -2905,67 +2912,67 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" t="s">
+        <v>53</v>
+      </c>
+      <c r="I22" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" t="s">
         <v>47</v>
-      </c>
-      <c r="E22" t="s">
-        <v>67</v>
-      </c>
-      <c r="F22" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" t="s">
-        <v>60</v>
-      </c>
-      <c r="H22" t="s">
-        <v>83</v>
-      </c>
-      <c r="I22" t="s">
-        <v>77</v>
-      </c>
-      <c r="J22" t="s">
-        <v>51</v>
       </c>
       <c r="K22" t="s">
         <v>50</v>
       </c>
       <c r="L22" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M22" t="s">
+        <v>140</v>
+      </c>
+      <c r="N22" t="s">
+        <v>146</v>
+      </c>
+      <c r="O22" t="s">
+        <v>84</v>
+      </c>
+      <c r="P22" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>1</v>
+      </c>
+      <c r="R22" t="s">
+        <v>1</v>
+      </c>
+      <c r="S22" t="s">
+        <v>147</v>
+      </c>
+      <c r="T22" t="s">
+        <v>148</v>
+      </c>
+      <c r="U22" t="s">
+        <v>1</v>
+      </c>
+      <c r="V22" t="s">
         <v>149</v>
       </c>
-      <c r="N22" t="s">
-        <v>69</v>
-      </c>
-      <c r="O22" t="s">
-        <v>90</v>
-      </c>
-      <c r="P22" t="s">
+      <c r="W22" t="s">
         <v>150</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>1</v>
-      </c>
-      <c r="R22" t="s">
-        <v>1</v>
-      </c>
-      <c r="S22" t="s">
-        <v>151</v>
-      </c>
-      <c r="T22" t="s">
-        <v>152</v>
-      </c>
-      <c r="U22" t="s">
-        <v>1</v>
-      </c>
-      <c r="V22" t="s">
-        <v>153</v>
-      </c>
-      <c r="W22" t="s">
-        <v>154</v>
       </c>
       <c r="X22" t="s">
         <v>1</v>
@@ -2974,7 +2981,7 @@
         <v>3</v>
       </c>
       <c r="Z22" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AA22" t="s">
         <v>1</v>
@@ -2988,46 +2995,46 @@
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="E23" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G23" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="I23" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J23" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="K23" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="L23" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="M23" t="s">
-        <v>149</v>
+        <v>69</v>
       </c>
       <c r="N23" t="s">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="O23" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="P23" t="s">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="Q23" t="s">
         <v>1</v>
@@ -3036,19 +3043,19 @@
         <v>1</v>
       </c>
       <c r="S23" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="T23" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="U23" t="s">
         <v>1</v>
       </c>
       <c r="V23" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="W23" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="X23" t="s">
         <v>1</v>
@@ -3057,7 +3064,7 @@
         <v>4</v>
       </c>
       <c r="Z23" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AA23" t="s">
         <v>1</v>
@@ -3065,52 +3072,52 @@
     </row>
     <row r="24" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s">
         <v>23</v>
       </c>
       <c r="G24" t="s">
+        <v>109</v>
+      </c>
+      <c r="H24" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" t="s">
         <v>34</v>
       </c>
-      <c r="H24" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="L24" t="s">
         <v>29</v>
       </c>
-      <c r="J24" t="s">
-        <v>28</v>
-      </c>
-      <c r="K24" t="s">
-        <v>31</v>
-      </c>
-      <c r="L24" t="s">
-        <v>51</v>
-      </c>
       <c r="M24" t="s">
+        <v>25</v>
+      </c>
+      <c r="N24" t="s">
+        <v>158</v>
+      </c>
+      <c r="O24" t="s">
         <v>30</v>
       </c>
-      <c r="N24" t="s">
-        <v>150</v>
-      </c>
-      <c r="O24" t="s">
-        <v>68</v>
-      </c>
       <c r="P24" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q24" t="s">
         <v>1</v>
@@ -3119,19 +3126,19 @@
         <v>1</v>
       </c>
       <c r="S24" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="T24" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="U24" t="s">
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="W24" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="X24" t="s">
         <v>1</v>
@@ -3140,7 +3147,7 @@
         <v>5</v>
       </c>
       <c r="Z24" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AA24" t="s">
         <v>1</v>
@@ -3154,46 +3161,46 @@
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E25" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s">
         <v>23</v>
       </c>
       <c r="G25" t="s">
+        <v>109</v>
+      </c>
+      <c r="H25" t="s">
+        <v>53</v>
+      </c>
+      <c r="I25" t="s">
+        <v>28</v>
+      </c>
+      <c r="J25" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" t="s">
         <v>34</v>
       </c>
-      <c r="H25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="L25" t="s">
         <v>29</v>
       </c>
-      <c r="J25" t="s">
-        <v>28</v>
-      </c>
-      <c r="K25" t="s">
-        <v>31</v>
-      </c>
-      <c r="L25" t="s">
-        <v>51</v>
-      </c>
       <c r="M25" t="s">
+        <v>25</v>
+      </c>
+      <c r="N25" t="s">
+        <v>158</v>
+      </c>
+      <c r="O25" t="s">
         <v>30</v>
       </c>
-      <c r="N25" t="s">
-        <v>150</v>
-      </c>
-      <c r="O25" t="s">
-        <v>68</v>
-      </c>
       <c r="P25" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q25" t="s">
         <v>1</v>
@@ -3202,19 +3209,19 @@
         <v>1</v>
       </c>
       <c r="S25" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="T25" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="U25" t="s">
         <v>1</v>
       </c>
       <c r="V25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="W25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="X25" t="s">
         <v>1</v>
@@ -3223,7 +3230,7 @@
         <v>6</v>
       </c>
       <c r="Z25" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="AA25" t="s">
         <v>1</v>
@@ -3237,46 +3244,46 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" t="s">
+        <v>68</v>
+      </c>
+      <c r="H26" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" t="s">
+        <v>49</v>
+      </c>
+      <c r="J26" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" t="s">
+        <v>51</v>
+      </c>
+      <c r="M26" t="s">
         <v>25</v>
       </c>
-      <c r="D26" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F26" t="s">
-        <v>75</v>
-      </c>
-      <c r="G26" t="s">
-        <v>119</v>
-      </c>
-      <c r="H26" t="s">
+      <c r="N26" t="s">
+        <v>130</v>
+      </c>
+      <c r="O26" t="s">
         <v>30</v>
       </c>
-      <c r="I26" t="s">
-        <v>76</v>
-      </c>
-      <c r="J26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K26" t="s">
-        <v>31</v>
-      </c>
-      <c r="L26" t="s">
-        <v>32</v>
-      </c>
-      <c r="M26" t="s">
-        <v>34</v>
-      </c>
-      <c r="N26" t="s">
-        <v>27</v>
-      </c>
-      <c r="O26" t="s">
-        <v>68</v>
-      </c>
       <c r="P26" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="Q26" t="s">
         <v>1</v>
@@ -3285,19 +3292,19 @@
         <v>1</v>
       </c>
       <c r="S26" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="T26" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="U26" t="s">
         <v>1</v>
       </c>
       <c r="V26" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="W26" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="X26" t="s">
         <v>1</v>
@@ -3306,7 +3313,7 @@
         <v>7</v>
       </c>
       <c r="Z26" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AA26" t="s">
         <v>1</v>
@@ -3320,46 +3327,46 @@
         <v>4</v>
       </c>
       <c r="C27" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" t="s">
+        <v>49</v>
+      </c>
+      <c r="J27" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L27" t="s">
         <v>51</v>
       </c>
-      <c r="D27" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" t="s">
-        <v>50</v>
-      </c>
-      <c r="F27" t="s">
-        <v>178</v>
-      </c>
-      <c r="G27" t="s">
-        <v>99</v>
-      </c>
-      <c r="H27" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" t="s">
-        <v>76</v>
-      </c>
-      <c r="J27" t="s">
-        <v>47</v>
-      </c>
-      <c r="K27" t="s">
-        <v>36</v>
-      </c>
-      <c r="L27" t="s">
-        <v>32</v>
-      </c>
       <c r="M27" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="N27" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="O27" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="P27" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="Q27" t="s">
         <v>1</v>
@@ -3368,19 +3375,19 @@
         <v>1</v>
       </c>
       <c r="S27" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="T27" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="U27" t="s">
         <v>1</v>
       </c>
       <c r="V27" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="W27" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="X27" t="s">
         <v>1</v>
@@ -3389,7 +3396,7 @@
         <v>8</v>
       </c>
       <c r="Z27" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="AA27" t="s">
         <v>1</v>
@@ -3403,46 +3410,46 @@
         <v>5</v>
       </c>
       <c r="C28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" t="s">
+        <v>179</v>
+      </c>
+      <c r="F28" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" t="s">
+        <v>86</v>
+      </c>
+      <c r="J28" t="s">
+        <v>28</v>
+      </c>
+      <c r="K28" t="s">
+        <v>52</v>
+      </c>
+      <c r="L28" t="s">
         <v>51</v>
       </c>
-      <c r="D28" t="s">
-        <v>50</v>
-      </c>
-      <c r="E28" t="s">
-        <v>24</v>
-      </c>
-      <c r="F28" t="s">
-        <v>178</v>
-      </c>
-      <c r="G28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I28" t="s">
-        <v>76</v>
-      </c>
-      <c r="J28" t="s">
-        <v>156</v>
-      </c>
-      <c r="K28" t="s">
-        <v>36</v>
-      </c>
-      <c r="L28" t="s">
-        <v>58</v>
-      </c>
       <c r="M28" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="N28" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="O28" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="P28" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="Q28" t="s">
         <v>1</v>
@@ -3451,19 +3458,19 @@
         <v>1</v>
       </c>
       <c r="S28" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="T28" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="U28" t="s">
         <v>1</v>
       </c>
       <c r="V28" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="W28" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="X28" t="s">
         <v>1</v>
@@ -3472,7 +3479,7 @@
         <v>9</v>
       </c>
       <c r="Z28" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AA28" t="s">
         <v>1</v>
@@ -3486,46 +3493,46 @@
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="D29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" t="s">
+        <v>179</v>
+      </c>
+      <c r="F29" t="s">
+        <v>66</v>
+      </c>
+      <c r="G29" t="s">
+        <v>60</v>
+      </c>
+      <c r="H29" t="s">
+        <v>94</v>
+      </c>
+      <c r="I29" t="s">
+        <v>86</v>
+      </c>
+      <c r="J29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K29" t="s">
+        <v>52</v>
+      </c>
+      <c r="L29" t="s">
         <v>50</v>
       </c>
-      <c r="E29" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" t="s">
-        <v>67</v>
-      </c>
-      <c r="G29" t="s">
-        <v>119</v>
-      </c>
-      <c r="H29" t="s">
-        <v>184</v>
-      </c>
-      <c r="I29" t="s">
-        <v>26</v>
-      </c>
-      <c r="J29" t="s">
-        <v>76</v>
-      </c>
-      <c r="K29" t="s">
-        <v>156</v>
-      </c>
-      <c r="L29" t="s">
-        <v>58</v>
-      </c>
       <c r="M29" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="N29" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O29" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="P29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q29" t="s">
         <v>1</v>
@@ -3534,19 +3541,19 @@
         <v>1</v>
       </c>
       <c r="S29" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="T29" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="U29" t="s">
         <v>1</v>
       </c>
       <c r="V29" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W29" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="X29" t="s">
         <v>1</v>
@@ -3569,46 +3576,46 @@
         <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" t="s">
-        <v>51</v>
+        <v>85</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="F30" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" t="s">
         <v>60</v>
       </c>
-      <c r="G30" t="s">
-        <v>91</v>
-      </c>
       <c r="H30" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="I30" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="K30" t="s">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="L30" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M30" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="N30" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O30" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="P30" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="Q30" t="s">
         <v>1</v>
@@ -3617,25 +3624,25 @@
         <v>1</v>
       </c>
       <c r="S30" t="s">
+        <v>191</v>
+      </c>
+      <c r="T30" t="s">
+        <v>192</v>
+      </c>
+      <c r="U30" t="s">
+        <v>1</v>
+      </c>
+      <c r="V30" t="s">
+        <v>193</v>
+      </c>
+      <c r="W30" t="s">
         <v>194</v>
       </c>
-      <c r="T30" t="s">
+      <c r="X30" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="s">
         <v>195</v>
-      </c>
-      <c r="U30" t="s">
-        <v>1</v>
-      </c>
-      <c r="V30" t="s">
-        <v>196</v>
-      </c>
-      <c r="W30" t="s">
-        <v>197</v>
-      </c>
-      <c r="X30" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>198</v>
       </c>
       <c r="Z30" t="s">
         <v>1</v>
@@ -3652,46 +3659,46 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" t="s">
+        <v>102</v>
+      </c>
+      <c r="F31" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H31" t="s">
         <v>48</v>
       </c>
-      <c r="D31" t="s">
-        <v>51</v>
-      </c>
-      <c r="E31" t="s">
-        <v>75</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31" t="s">
-        <v>91</v>
-      </c>
-      <c r="H31" t="s">
-        <v>26</v>
-      </c>
-      <c r="I31" t="s">
-        <v>184</v>
+      <c r="I31" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="J31" t="s">
+        <v>190</v>
+      </c>
+      <c r="K31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L31" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" t="s">
         <v>76</v>
       </c>
-      <c r="K31" t="s">
-        <v>47</v>
-      </c>
-      <c r="L31" t="s">
-        <v>67</v>
-      </c>
-      <c r="M31" t="s">
-        <v>49</v>
-      </c>
       <c r="N31" t="s">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="O31" t="s">
-        <v>100</v>
+        <v>196</v>
       </c>
       <c r="P31" t="s">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="Q31" t="s">
         <v>1</v>
@@ -3700,19 +3707,19 @@
         <v>1</v>
       </c>
       <c r="S31" t="s">
+        <v>197</v>
+      </c>
+      <c r="T31" t="s">
+        <v>198</v>
+      </c>
+      <c r="U31" t="s">
+        <v>1</v>
+      </c>
+      <c r="V31" t="s">
         <v>199</v>
       </c>
-      <c r="T31" t="s">
+      <c r="W31" t="s">
         <v>200</v>
-      </c>
-      <c r="U31" t="s">
-        <v>1</v>
-      </c>
-      <c r="V31" t="s">
-        <v>201</v>
-      </c>
-      <c r="W31" t="s">
-        <v>202</v>
       </c>
       <c r="X31" t="s">
         <v>1</v>
@@ -3735,46 +3742,46 @@
         <v>9</v>
       </c>
       <c r="C32" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" t="s">
+        <v>85</v>
+      </c>
+      <c r="F32" t="s">
+        <v>67</v>
+      </c>
+      <c r="G32" t="s">
+        <v>51</v>
+      </c>
+      <c r="H32" t="s">
         <v>48</v>
       </c>
-      <c r="D32" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
-        <v>75</v>
-      </c>
-      <c r="F32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" t="s">
-        <v>91</v>
-      </c>
-      <c r="H32" t="s">
-        <v>26</v>
-      </c>
       <c r="I32" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="J32" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="K32" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="L32" t="s">
-        <v>67</v>
+        <v>202</v>
       </c>
       <c r="M32" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="N32" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="O32" t="s">
-        <v>90</v>
+        <v>196</v>
       </c>
       <c r="P32" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="Q32" t="s">
         <v>1</v>
@@ -3804,7 +3811,7 @@
         <v>1</v>
       </c>
       <c r="Z32" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AA32" t="s">
         <v>1</v>
@@ -3818,46 +3825,46 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" t="s">
         <v>27</v>
       </c>
-      <c r="D33" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
+        <v>60</v>
+      </c>
+      <c r="G33" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" t="s">
+        <v>28</v>
+      </c>
+      <c r="J33" t="s">
+        <v>23</v>
+      </c>
+      <c r="K33" t="s">
+        <v>30</v>
+      </c>
+      <c r="L33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M33" t="s">
+        <v>33</v>
+      </c>
+      <c r="N33" t="s">
+        <v>47</v>
+      </c>
+      <c r="O33" t="s">
+        <v>29</v>
+      </c>
+      <c r="P33" t="s">
         <v>34</v>
-      </c>
-      <c r="F33" t="s">
-        <v>36</v>
-      </c>
-      <c r="G33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H33" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" t="s">
-        <v>125</v>
-      </c>
-      <c r="J33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" t="s">
-        <v>28</v>
-      </c>
-      <c r="L33" t="s">
-        <v>29</v>
-      </c>
-      <c r="M33" t="s">
-        <v>100</v>
-      </c>
-      <c r="N33" t="s">
-        <v>120</v>
-      </c>
-      <c r="O33" t="s">
-        <v>60</v>
-      </c>
-      <c r="P33" t="s">
-        <v>35</v>
       </c>
       <c r="Q33" t="s">
         <v>1</v>
@@ -3887,7 +3894,7 @@
         <v>2</v>
       </c>
       <c r="Z33" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AA33" t="s">
         <v>1</v>
@@ -3901,46 +3908,46 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" t="s">
         <v>27</v>
       </c>
-      <c r="D34" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
+        <v>60</v>
+      </c>
+      <c r="G34" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34" t="s">
+        <v>28</v>
+      </c>
+      <c r="J34" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" t="s">
+        <v>30</v>
+      </c>
+      <c r="L34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M34" t="s">
+        <v>33</v>
+      </c>
+      <c r="N34" t="s">
+        <v>47</v>
+      </c>
+      <c r="O34" t="s">
+        <v>29</v>
+      </c>
+      <c r="P34" t="s">
         <v>34</v>
-      </c>
-      <c r="F34" t="s">
-        <v>36</v>
-      </c>
-      <c r="G34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H34" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" t="s">
-        <v>125</v>
-      </c>
-      <c r="J34" t="s">
-        <v>31</v>
-      </c>
-      <c r="K34" t="s">
-        <v>28</v>
-      </c>
-      <c r="L34" t="s">
-        <v>29</v>
-      </c>
-      <c r="M34" t="s">
-        <v>100</v>
-      </c>
-      <c r="N34" t="s">
-        <v>120</v>
-      </c>
-      <c r="O34" t="s">
-        <v>60</v>
-      </c>
-      <c r="P34" t="s">
-        <v>35</v>
       </c>
       <c r="Q34" t="s">
         <v>1</v>
@@ -3970,7 +3977,7 @@
         <v>3</v>
       </c>
       <c r="Z34" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AA34" t="s">
         <v>1</v>
@@ -3984,46 +3991,46 @@
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="G35" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="I35" t="s">
-        <v>216</v>
+        <v>59</v>
       </c>
       <c r="J35" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K35" t="s">
         <v>34</v>
       </c>
       <c r="L35" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M35" t="s">
-        <v>126</v>
-      </c>
-      <c r="N35" t="s">
-        <v>90</v>
+        <v>25</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="P35" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="Q35" t="s">
         <v>1</v>
@@ -4032,19 +4039,19 @@
         <v>1</v>
       </c>
       <c r="S35" t="s">
+        <v>216</v>
+      </c>
+      <c r="T35" t="s">
         <v>217</v>
       </c>
-      <c r="T35" t="s">
+      <c r="U35" t="s">
+        <v>1</v>
+      </c>
+      <c r="V35" t="s">
         <v>218</v>
       </c>
-      <c r="U35" t="s">
-        <v>1</v>
-      </c>
-      <c r="V35" t="s">
+      <c r="W35" t="s">
         <v>219</v>
-      </c>
-      <c r="W35" t="s">
-        <v>220</v>
       </c>
       <c r="X35" t="s">
         <v>1</v>
@@ -4053,7 +4060,7 @@
         <v>4</v>
       </c>
       <c r="Z35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA35" t="s">
         <v>1</v>
@@ -4067,46 +4074,46 @@
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F36" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="G36" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="I36" t="s">
-        <v>216</v>
+        <v>59</v>
       </c>
       <c r="J36" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="K36" t="s">
         <v>34</v>
       </c>
       <c r="L36" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="M36" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="N36" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="O36" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="P36" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="Q36" t="s">
         <v>1</v>
@@ -4115,19 +4122,19 @@
         <v>1</v>
       </c>
       <c r="S36" t="s">
+        <v>220</v>
+      </c>
+      <c r="T36" t="s">
         <v>221</v>
       </c>
-      <c r="T36" t="s">
+      <c r="U36" t="s">
+        <v>1</v>
+      </c>
+      <c r="V36" t="s">
         <v>222</v>
       </c>
-      <c r="U36" t="s">
-        <v>1</v>
-      </c>
-      <c r="V36" t="s">
+      <c r="W36" t="s">
         <v>223</v>
-      </c>
-      <c r="W36" t="s">
-        <v>224</v>
       </c>
       <c r="X36" t="s">
         <v>1</v>
@@ -4136,7 +4143,7 @@
         <v>5</v>
       </c>
       <c r="Z36" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AA36" t="s">
         <v>1</v>
@@ -4150,46 +4157,46 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="D37" t="s">
-        <v>48</v>
+        <v>224</v>
       </c>
       <c r="E37" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="F37" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="G37" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" t="s">
+        <v>87</v>
+      </c>
+      <c r="I37" t="s">
+        <v>202</v>
+      </c>
+      <c r="J37" t="s">
+        <v>50</v>
+      </c>
+      <c r="K37" t="s">
+        <v>51</v>
+      </c>
+      <c r="L37" t="s">
         <v>30</v>
       </c>
-      <c r="H37" t="s">
-        <v>47</v>
-      </c>
-      <c r="I37" t="s">
-        <v>216</v>
-      </c>
-      <c r="J37" t="s">
-        <v>68</v>
-      </c>
-      <c r="K37" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" t="s">
-        <v>1</v>
-      </c>
       <c r="M37" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="N37" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="O37" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="P37" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="Q37" t="s">
         <v>1</v>
@@ -4233,46 +4240,46 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="E38" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G38" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="H38" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="I38" t="s">
+        <v>202</v>
+      </c>
+      <c r="J38" t="s">
         <v>229</v>
       </c>
-      <c r="J38" t="s">
-        <v>68</v>
-      </c>
       <c r="K38" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="L38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M38" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="N38" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="O38" t="s">
-        <v>216</v>
+        <v>59</v>
       </c>
       <c r="P38" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="Q38" t="s">
         <v>1</v>
@@ -4316,46 +4323,46 @@
         <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>179</v>
       </c>
       <c r="D39" t="s">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="E39" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="F39" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="G39" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="H39" t="s">
-        <v>58</v>
+        <v>201</v>
       </c>
       <c r="I39" t="s">
+        <v>48</v>
+      </c>
+      <c r="J39" t="s">
         <v>229</v>
-      </c>
-      <c r="J39" t="s">
-        <v>234</v>
       </c>
       <c r="K39" t="s">
         <v>51</v>
       </c>
       <c r="L39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M39" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="N39" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="O39" t="s">
-        <v>216</v>
+        <v>59</v>
       </c>
       <c r="P39" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="Q39" t="s">
         <v>1</v>
@@ -4364,10 +4371,10 @@
         <v>1</v>
       </c>
       <c r="S39" t="s">
+        <v>234</v>
+      </c>
+      <c r="T39" t="s">
         <v>235</v>
-      </c>
-      <c r="T39" t="s">
-        <v>236</v>
       </c>
       <c r="U39" t="s">
         <v>1</v>
@@ -4399,46 +4406,46 @@
         <v>8</v>
       </c>
       <c r="C40" t="s">
+        <v>179</v>
+      </c>
+      <c r="D40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" t="s">
+        <v>102</v>
+      </c>
+      <c r="F40" t="s">
+        <v>94</v>
+      </c>
+      <c r="G40" t="s">
+        <v>85</v>
+      </c>
+      <c r="H40" t="s">
+        <v>59</v>
+      </c>
+      <c r="I40" t="s">
+        <v>86</v>
+      </c>
+      <c r="J40" t="s">
+        <v>201</v>
+      </c>
+      <c r="K40" t="s">
+        <v>48</v>
+      </c>
+      <c r="L40" t="s">
+        <v>67</v>
+      </c>
+      <c r="M40" t="s">
+        <v>96</v>
+      </c>
+      <c r="N40" t="s">
+        <v>36</v>
+      </c>
+      <c r="O40" t="s">
         <v>84</v>
       </c>
-      <c r="D40" t="s">
-        <v>98</v>
-      </c>
-      <c r="E40" t="s">
-        <v>30</v>
-      </c>
-      <c r="F40" t="s">
-        <v>49</v>
-      </c>
-      <c r="G40" t="s">
-        <v>75</v>
-      </c>
-      <c r="H40" t="s">
-        <v>58</v>
-      </c>
-      <c r="I40" t="s">
-        <v>229</v>
-      </c>
-      <c r="J40" t="s">
-        <v>234</v>
-      </c>
-      <c r="K40" t="s">
-        <v>51</v>
-      </c>
-      <c r="L40" t="s">
-        <v>184</v>
-      </c>
-      <c r="M40" t="s">
-        <v>150</v>
-      </c>
-      <c r="N40" t="s">
-        <v>138</v>
-      </c>
-      <c r="O40" t="s">
-        <v>60</v>
-      </c>
       <c r="P40" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="Q40" t="s">
         <v>1</v>
@@ -4447,10 +4454,10 @@
         <v>1</v>
       </c>
       <c r="S40" t="s">
+        <v>236</v>
+      </c>
+      <c r="T40" t="s">
         <v>237</v>
-      </c>
-      <c r="T40" t="s">
-        <v>238</v>
       </c>
       <c r="U40" t="s">
         <v>1</v>
@@ -4482,46 +4489,46 @@
         <v>9</v>
       </c>
       <c r="C41" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" t="s">
+        <v>102</v>
+      </c>
+      <c r="F41" t="s">
+        <v>94</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>59</v>
+      </c>
+      <c r="I41" t="s">
+        <v>86</v>
+      </c>
+      <c r="J41" t="s">
+        <v>201</v>
+      </c>
+      <c r="K41" t="s">
+        <v>48</v>
+      </c>
+      <c r="L41" t="s">
+        <v>67</v>
+      </c>
+      <c r="M41" t="s">
+        <v>96</v>
+      </c>
+      <c r="N41" t="s">
+        <v>36</v>
+      </c>
+      <c r="O41" t="s">
         <v>84</v>
       </c>
-      <c r="D41" t="s">
-        <v>98</v>
-      </c>
-      <c r="E41" t="s">
-        <v>30</v>
-      </c>
-      <c r="F41" t="s">
-        <v>49</v>
-      </c>
-      <c r="G41" t="s">
-        <v>75</v>
-      </c>
-      <c r="H41" t="s">
-        <v>58</v>
-      </c>
-      <c r="I41" t="s">
-        <v>47</v>
-      </c>
-      <c r="J41" t="s">
-        <v>1</v>
-      </c>
-      <c r="K41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L41" t="s">
-        <v>184</v>
-      </c>
-      <c r="M41" t="s">
-        <v>150</v>
-      </c>
-      <c r="N41" t="s">
-        <v>138</v>
-      </c>
-      <c r="O41" t="s">
-        <v>60</v>
-      </c>
       <c r="P41" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="Q41" t="s">
         <v>1</v>
@@ -4530,10 +4537,10 @@
         <v>1</v>
       </c>
       <c r="S41" t="s">
+        <v>238</v>
+      </c>
+      <c r="T41" t="s">
         <v>239</v>
-      </c>
-      <c r="T41" t="s">
-        <v>240</v>
       </c>
       <c r="U41" t="s">
         <v>1</v>
@@ -4559,52 +4566,52 @@
     </row>
     <row r="42" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>107</v>
+        <v>224</v>
       </c>
       <c r="D42" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" t="s">
         <v>27</v>
       </c>
-      <c r="E42" t="s">
-        <v>23</v>
-      </c>
-      <c r="F42" t="s">
-        <v>25</v>
-      </c>
       <c r="G42" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I42" t="s">
         <v>32</v>
       </c>
       <c r="J42" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="K42" t="s">
         <v>28</v>
       </c>
       <c r="L42" t="s">
+        <v>94</v>
+      </c>
+      <c r="M42" t="s">
         <v>29</v>
       </c>
-      <c r="M42" t="s">
-        <v>35</v>
-      </c>
       <c r="N42" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O42" t="s">
-        <v>216</v>
+        <v>33</v>
       </c>
       <c r="P42" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="Q42" t="s">
         <v>1</v>
@@ -4613,10 +4620,10 @@
         <v>1</v>
       </c>
       <c r="S42" t="s">
+        <v>241</v>
+      </c>
+      <c r="T42" t="s">
         <v>242</v>
-      </c>
-      <c r="T42" t="s">
-        <v>243</v>
       </c>
       <c r="U42" t="s">
         <v>1</v>
@@ -4648,46 +4655,46 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>224</v>
       </c>
       <c r="D43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" t="s">
         <v>27</v>
       </c>
-      <c r="E43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F43" t="s">
-        <v>25</v>
-      </c>
       <c r="G43" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I43" t="s">
         <v>32</v>
       </c>
       <c r="J43" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="K43" t="s">
         <v>28</v>
       </c>
       <c r="L43" t="s">
+        <v>94</v>
+      </c>
+      <c r="M43" t="s">
         <v>29</v>
       </c>
-      <c r="M43" t="s">
-        <v>35</v>
-      </c>
       <c r="N43" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O43" t="s">
-        <v>216</v>
+        <v>33</v>
       </c>
       <c r="P43" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="Q43" t="s">
         <v>1</v>
@@ -4696,10 +4703,10 @@
         <v>1</v>
       </c>
       <c r="S43" t="s">
+        <v>243</v>
+      </c>
+      <c r="T43" t="s">
         <v>244</v>
-      </c>
-      <c r="T43" t="s">
-        <v>245</v>
       </c>
       <c r="U43" t="s">
         <v>1</v>
@@ -4731,46 +4738,46 @@
         <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>36</v>
+        <v>224</v>
       </c>
       <c r="D44" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="E44" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="F44" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G44" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" t="s">
+        <v>50</v>
+      </c>
+      <c r="I44" t="s">
+        <v>75</v>
+      </c>
+      <c r="J44" t="s">
         <v>23</v>
       </c>
-      <c r="H44" t="s">
-        <v>33</v>
-      </c>
-      <c r="I44" t="s">
-        <v>229</v>
-      </c>
-      <c r="J44" t="s">
-        <v>27</v>
-      </c>
       <c r="K44" t="s">
+        <v>29</v>
+      </c>
+      <c r="L44" t="s">
         <v>28</v>
       </c>
-      <c r="L44" t="s">
-        <v>26</v>
-      </c>
       <c r="M44" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="N44" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O44" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="P44" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="Q44" t="s">
         <v>1</v>
@@ -4814,46 +4821,46 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D45" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="E45" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="F45" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="G45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H45" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I45" t="s">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="J45" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="L45" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M45" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="N45" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="O45" t="s">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="P45" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="Q45" t="s">
         <v>1</v>
@@ -4897,46 +4904,46 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" t="s">
+        <v>85</v>
+      </c>
+      <c r="E46" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" t="s">
+        <v>47</v>
+      </c>
+      <c r="G46" t="s">
+        <v>29</v>
+      </c>
+      <c r="H46" t="s">
+        <v>50</v>
+      </c>
+      <c r="I46" t="s">
         <v>75</v>
       </c>
-      <c r="D46" t="s">
-        <v>57</v>
-      </c>
-      <c r="E46" t="s">
-        <v>99</v>
-      </c>
-      <c r="F46" t="s">
-        <v>107</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="J46" t="s">
+        <v>94</v>
+      </c>
+      <c r="K46" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" t="s">
+        <v>202</v>
+      </c>
+      <c r="M46" t="s">
+        <v>30</v>
+      </c>
+      <c r="N46" t="s">
+        <v>59</v>
+      </c>
+      <c r="O46" t="s">
+        <v>196</v>
+      </c>
+      <c r="P46" t="s">
         <v>67</v>
-      </c>
-      <c r="H46" t="s">
-        <v>34</v>
-      </c>
-      <c r="I46" t="s">
-        <v>84</v>
-      </c>
-      <c r="J46" t="s">
-        <v>32</v>
-      </c>
-      <c r="K46" t="s">
-        <v>47</v>
-      </c>
-      <c r="L46" t="s">
-        <v>77</v>
-      </c>
-      <c r="M46" t="s">
-        <v>83</v>
-      </c>
-      <c r="N46" t="s">
-        <v>30</v>
-      </c>
-      <c r="O46" t="s">
-        <v>126</v>
-      </c>
-      <c r="P46" t="s">
-        <v>59</v>
       </c>
       <c r="Q46" t="s">
         <v>1</v>
@@ -4974,52 +4981,52 @@
     </row>
     <row r="47" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F47" t="s">
+        <v>49</v>
+      </c>
+      <c r="G47" t="s">
+        <v>94</v>
+      </c>
+      <c r="H47" t="s">
+        <v>28</v>
+      </c>
+      <c r="I47" t="s">
+        <v>120</v>
+      </c>
+      <c r="J47" t="s">
         <v>34</v>
       </c>
-      <c r="D47" t="s">
+      <c r="K47" t="s">
+        <v>201</v>
+      </c>
+      <c r="L47" t="s">
+        <v>52</v>
+      </c>
+      <c r="M47" t="s">
+        <v>185</v>
+      </c>
+      <c r="N47" t="s">
         <v>23</v>
       </c>
-      <c r="E47" t="s">
-        <v>47</v>
-      </c>
-      <c r="F47" t="s">
-        <v>50</v>
-      </c>
-      <c r="G47" t="s">
-        <v>36</v>
-      </c>
-      <c r="H47" t="s">
-        <v>125</v>
-      </c>
-      <c r="I47" t="s">
-        <v>30</v>
-      </c>
-      <c r="J47" t="s">
-        <v>48</v>
-      </c>
-      <c r="K47" t="s">
-        <v>32</v>
-      </c>
-      <c r="L47" t="s">
-        <v>68</v>
-      </c>
-      <c r="M47" t="s">
-        <v>35</v>
-      </c>
-      <c r="N47" t="s">
-        <v>27</v>
-      </c>
       <c r="O47" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="P47" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q47" t="s">
         <v>1</v>
@@ -5063,46 +5070,46 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" t="s">
+        <v>51</v>
+      </c>
+      <c r="F48" t="s">
+        <v>49</v>
+      </c>
+      <c r="G48" t="s">
+        <v>94</v>
+      </c>
+      <c r="H48" t="s">
+        <v>28</v>
+      </c>
+      <c r="I48" t="s">
+        <v>120</v>
+      </c>
+      <c r="J48" t="s">
         <v>34</v>
       </c>
-      <c r="D48" t="s">
+      <c r="K48" t="s">
+        <v>201</v>
+      </c>
+      <c r="L48" t="s">
+        <v>52</v>
+      </c>
+      <c r="M48" t="s">
+        <v>185</v>
+      </c>
+      <c r="N48" t="s">
         <v>23</v>
       </c>
-      <c r="E48" t="s">
-        <v>47</v>
-      </c>
-      <c r="F48" t="s">
-        <v>50</v>
-      </c>
-      <c r="G48" t="s">
-        <v>36</v>
-      </c>
-      <c r="H48" t="s">
-        <v>125</v>
-      </c>
-      <c r="I48" t="s">
-        <v>30</v>
-      </c>
-      <c r="J48" t="s">
-        <v>48</v>
-      </c>
-      <c r="K48" t="s">
-        <v>32</v>
-      </c>
-      <c r="L48" t="s">
-        <v>68</v>
-      </c>
-      <c r="M48" t="s">
-        <v>35</v>
-      </c>
-      <c r="N48" t="s">
-        <v>27</v>
-      </c>
       <c r="O48" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="P48" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q48" t="s">
         <v>1</v>
@@ -5146,46 +5153,46 @@
         <v>3</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="E49" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="F49" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G49" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="H49" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="I49" t="s">
+        <v>77</v>
+      </c>
+      <c r="J49" t="s">
         <v>34</v>
       </c>
-      <c r="J49" t="s">
-        <v>31</v>
-      </c>
       <c r="K49" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="L49" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="M49" t="s">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="N49" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="O49" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="P49" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="Q49" t="s">
         <v>1</v>
@@ -5229,46 +5236,46 @@
         <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D50" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="E50" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" t="s">
+        <v>52</v>
+      </c>
+      <c r="H50" t="s">
+        <v>30</v>
+      </c>
+      <c r="I50" t="s">
+        <v>77</v>
+      </c>
+      <c r="J50" t="s">
+        <v>49</v>
+      </c>
+      <c r="K50" t="s">
+        <v>28</v>
+      </c>
+      <c r="L50" t="s">
         <v>51</v>
       </c>
-      <c r="F50" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" t="s">
-        <v>107</v>
-      </c>
-      <c r="H50" t="s">
-        <v>76</v>
-      </c>
-      <c r="I50" t="s">
-        <v>34</v>
-      </c>
-      <c r="J50" t="s">
-        <v>31</v>
-      </c>
-      <c r="K50" t="s">
-        <v>68</v>
-      </c>
-      <c r="L50" t="s">
-        <v>36</v>
-      </c>
       <c r="M50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="N50" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="O50" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="P50" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="Q50" t="s">
         <v>1</v>
@@ -5312,46 +5319,46 @@
         <v>5</v>
       </c>
       <c r="C51" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" t="s">
+        <v>93</v>
+      </c>
+      <c r="E51" t="s">
+        <v>66</v>
+      </c>
+      <c r="F51" t="s">
+        <v>246</v>
+      </c>
+      <c r="G51" t="s">
+        <v>52</v>
+      </c>
+      <c r="H51" t="s">
+        <v>202</v>
+      </c>
+      <c r="I51" t="s">
+        <v>30</v>
+      </c>
+      <c r="J51" t="s">
+        <v>49</v>
+      </c>
+      <c r="K51" t="s">
+        <v>94</v>
+      </c>
+      <c r="L51" t="s">
+        <v>51</v>
+      </c>
+      <c r="M51" t="s">
         <v>60</v>
       </c>
-      <c r="D51" t="s">
-        <v>75</v>
-      </c>
-      <c r="E51" t="s">
-        <v>107</v>
-      </c>
-      <c r="F51" t="s">
-        <v>30</v>
-      </c>
-      <c r="G51" t="s">
-        <v>59</v>
-      </c>
-      <c r="H51" t="s">
+      <c r="N51" t="s">
+        <v>140</v>
+      </c>
+      <c r="O51" t="s">
+        <v>77</v>
+      </c>
+      <c r="P51" t="s">
         <v>76</v>
-      </c>
-      <c r="I51" t="s">
-        <v>68</v>
-      </c>
-      <c r="J51" t="s">
-        <v>84</v>
-      </c>
-      <c r="K51" t="s">
-        <v>234</v>
-      </c>
-      <c r="L51" t="s">
-        <v>125</v>
-      </c>
-      <c r="M51" t="s">
-        <v>83</v>
-      </c>
-      <c r="N51" t="s">
-        <v>51</v>
-      </c>
-      <c r="O51" t="s">
-        <v>150</v>
-      </c>
-      <c r="P51" t="s">
-        <v>100</v>
       </c>
       <c r="Q51" t="s">
         <v>1</v>
@@ -5395,46 +5402,46 @@
         <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D52" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E52" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="F52" t="s">
+        <v>246</v>
+      </c>
+      <c r="G52" t="s">
+        <v>26</v>
+      </c>
+      <c r="H52" t="s">
+        <v>202</v>
+      </c>
+      <c r="I52" t="s">
         <v>30</v>
       </c>
-      <c r="G52" t="s">
-        <v>59</v>
-      </c>
-      <c r="H52" t="s">
-        <v>33</v>
-      </c>
-      <c r="I52" t="s">
-        <v>68</v>
-      </c>
       <c r="J52" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K52" t="s">
-        <v>234</v>
+        <v>94</v>
       </c>
       <c r="L52" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="M52" t="s">
         <v>69</v>
       </c>
       <c r="N52" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="O52" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="P52" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="Q52" t="s">
         <v>1</v>
@@ -5478,43 +5485,43 @@
         <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="D53" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="E53" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="F53" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="G53" t="s">
         <v>26</v>
       </c>
       <c r="H53" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="I53" t="s">
-        <v>216</v>
+        <v>47</v>
       </c>
       <c r="J53" t="s">
+        <v>87</v>
+      </c>
+      <c r="K53" t="s">
+        <v>229</v>
+      </c>
+      <c r="L53" t="s">
+        <v>120</v>
+      </c>
+      <c r="M53" t="s">
+        <v>59</v>
+      </c>
+      <c r="N53" t="s">
         <v>84</v>
       </c>
-      <c r="K53" t="s">
-        <v>30</v>
-      </c>
-      <c r="L53" t="s">
-        <v>47</v>
-      </c>
-      <c r="M53" t="s">
-        <v>69</v>
-      </c>
-      <c r="N53" t="s">
-        <v>100</v>
-      </c>
       <c r="O53" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P53" t="s">
         <v>67</v>
@@ -5561,43 +5568,43 @@
         <v>8</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="E54" t="s">
+        <v>93</v>
+      </c>
+      <c r="F54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G54" t="s">
+        <v>140</v>
+      </c>
+      <c r="H54" t="s">
+        <v>69</v>
+      </c>
+      <c r="I54" t="s">
+        <v>47</v>
+      </c>
+      <c r="J54" t="s">
+        <v>87</v>
+      </c>
+      <c r="K54" t="s">
+        <v>229</v>
+      </c>
+      <c r="L54" t="s">
         <v>48</v>
       </c>
-      <c r="F54" t="s">
-        <v>66</v>
-      </c>
-      <c r="G54" t="s">
-        <v>26</v>
-      </c>
-      <c r="H54" t="s">
-        <v>51</v>
-      </c>
-      <c r="I54" t="s">
-        <v>216</v>
-      </c>
-      <c r="J54" t="s">
-        <v>184</v>
-      </c>
-      <c r="K54" t="s">
-        <v>30</v>
-      </c>
-      <c r="L54" t="s">
-        <v>47</v>
-      </c>
       <c r="M54" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="N54" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="O54" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P54" t="s">
         <v>67</v>
@@ -5644,43 +5651,43 @@
         <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="D55" t="s">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="E55" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F55" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="G55" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="H55" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="I55" t="s">
         <v>48</v>
       </c>
       <c r="J55" t="s">
-        <v>184</v>
+        <v>86</v>
       </c>
       <c r="K55" t="s">
-        <v>58</v>
+        <v>190</v>
       </c>
       <c r="L55" t="s">
-        <v>50</v>
+        <v>201</v>
       </c>
       <c r="M55" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="N55" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="O55" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="P55" t="s">
         <v>67</v>
@@ -5726,47 +5733,47 @@
       <c r="B56">
         <v>10</v>
       </c>
-      <c r="C56" t="s">
-        <v>98</v>
+      <c r="C56" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E56" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F56" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="G56" t="s">
-        <v>49</v>
-      </c>
-      <c r="H56" t="s">
+        <v>35</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I56" t="s">
         <v>48</v>
       </c>
       <c r="J56" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K56" t="s">
-        <v>58</v>
+        <v>190</v>
       </c>
       <c r="L56" t="s">
-        <v>50</v>
+        <v>201</v>
       </c>
       <c r="M56" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="N56" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="O56" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="P56" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="Q56" t="s">
         <v>1</v>
